--- a/data/industry_cache/20260904/industry_observation.xlsx
+++ b/data/industry_cache/20260904/industry_observation.xlsx
@@ -545,19 +545,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1.2152</v>
+        <v>1.2382</v>
       </c>
       <c r="D2" t="n">
-        <v>42.69</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="E2" t="n">
-        <v>58.43</v>
+        <v>81.19</v>
       </c>
       <c r="F2" t="n">
-        <v>57.74</v>
+        <v>59.23</v>
       </c>
       <c r="G2" t="n">
-        <v>96.41</v>
+        <v>97.29000000000001</v>
       </c>
       <c r="H2" t="n">
         <v>0.58</v>
@@ -578,17 +578,17 @@
         <v>-9.41</v>
       </c>
       <c r="N2" t="n">
-        <v>6.46</v>
+        <v>3.87</v>
       </c>
       <c r="O2" t="n">
-        <v>7.93</v>
+        <v>7.94</v>
       </c>
       <c r="P2" t="n">
-        <v>-7.22</v>
+        <v>-9.470000000000001</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>平配</t>
+          <t>低配</t>
         </is>
       </c>
       <c r="R2" t="n">
@@ -601,10 +601,10 @@
         <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
@@ -624,19 +624,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>4.657</v>
+        <v>4.6221</v>
       </c>
       <c r="D3" t="n">
-        <v>30.24</v>
+        <v>26.66</v>
       </c>
       <c r="E3" t="n">
-        <v>89.39</v>
+        <v>75.73</v>
       </c>
       <c r="F3" t="n">
-        <v>44.64</v>
+        <v>47.12</v>
       </c>
       <c r="G3" t="n">
-        <v>70.65000000000001</v>
+        <v>77.63</v>
       </c>
       <c r="H3" t="n">
         <v>2.79</v>
@@ -657,13 +657,13 @@
         <v>1.25</v>
       </c>
       <c r="N3" t="n">
-        <v>3.4</v>
+        <v>1.56</v>
       </c>
       <c r="O3" t="n">
-        <v>8.91</v>
+        <v>1.92</v>
       </c>
       <c r="P3" t="n">
-        <v>17.02</v>
+        <v>11.27</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -680,10 +680,10 @@
         <v>1</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
@@ -703,19 +703,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.591</v>
+        <v>0.5908</v>
       </c>
       <c r="D4" t="n">
-        <v>29.91</v>
+        <v>31.45</v>
       </c>
       <c r="E4" t="n">
-        <v>77.04000000000001</v>
+        <v>79.84</v>
       </c>
       <c r="F4" t="n">
-        <v>20.73</v>
+        <v>21.78</v>
       </c>
       <c r="G4" t="n">
-        <v>41.95</v>
+        <v>44.9</v>
       </c>
       <c r="H4" t="n">
         <v>0.41</v>
@@ -736,17 +736,17 @@
         <v>-1.01</v>
       </c>
       <c r="N4" t="n">
-        <v>3.23</v>
+        <v>-0.79</v>
       </c>
       <c r="O4" t="n">
-        <v>1.05</v>
+        <v>-0.92</v>
       </c>
       <c r="P4" t="n">
-        <v>-7.91</v>
+        <v>-10.52</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>高配</t>
+          <t>低配</t>
         </is>
       </c>
       <c r="R4" t="n">
@@ -759,10 +759,10 @@
         <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="V4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
@@ -782,19 +782,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>5.6791</v>
+        <v>5.5357</v>
       </c>
       <c r="D5" t="n">
-        <v>22.51</v>
+        <v>18.66</v>
       </c>
       <c r="E5" t="n">
-        <v>64.77</v>
+        <v>34.55</v>
       </c>
       <c r="F5" t="n">
-        <v>48.93</v>
+        <v>50.61</v>
       </c>
       <c r="G5" t="n">
-        <v>77.27</v>
+        <v>79.86</v>
       </c>
       <c r="H5" t="n">
         <v>5.71</v>
@@ -815,17 +815,17 @@
         <v>4.6</v>
       </c>
       <c r="N5" t="n">
-        <v>1.68</v>
+        <v>-2.43</v>
       </c>
       <c r="O5" t="n">
-        <v>11.35</v>
+        <v>-0.26</v>
       </c>
       <c r="P5" t="n">
-        <v>51.35</v>
+        <v>41.6</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>高配</t>
+          <t>平配</t>
         </is>
       </c>
       <c r="R5" t="n">
@@ -838,10 +838,10 @@
         <v>1</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="V5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
@@ -861,19 +861,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>19.8026</v>
+        <v>19.5861</v>
       </c>
       <c r="D6" t="n">
-        <v>80.47</v>
+        <v>63.02</v>
       </c>
       <c r="E6" t="n">
-        <v>95.95999999999999</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="F6" t="n">
-        <v>55.94</v>
+        <v>51.61</v>
       </c>
       <c r="G6" t="n">
-        <v>82.93000000000001</v>
+        <v>79.3</v>
       </c>
       <c r="H6" t="n">
         <v>2.31</v>
@@ -894,13 +894,13 @@
         <v>7.53</v>
       </c>
       <c r="N6" t="n">
-        <v>0.15</v>
+        <v>-0.01</v>
       </c>
       <c r="O6" t="n">
-        <v>10.24</v>
+        <v>0.33</v>
       </c>
       <c r="P6" t="n">
-        <v>69.34</v>
+        <v>58.06</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         </is>
       </c>
       <c r="R6" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
@@ -917,7 +917,7 @@
         <v>1</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -940,19 +940,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>3.5901</v>
+        <v>3.6038</v>
       </c>
       <c r="D7" t="n">
-        <v>24.97</v>
+        <v>25.5</v>
       </c>
       <c r="E7" t="n">
-        <v>19.79</v>
+        <v>24.11</v>
       </c>
       <c r="F7" t="n">
-        <v>27.86</v>
+        <v>28.21</v>
       </c>
       <c r="G7" t="n">
-        <v>17.3</v>
+        <v>18.87</v>
       </c>
       <c r="H7" t="n">
         <v>2.86</v>
@@ -973,17 +973,17 @@
         <v>-0.87</v>
       </c>
       <c r="N7" t="n">
-        <v>1.11</v>
+        <v>0.01</v>
       </c>
       <c r="O7" t="n">
-        <v>0.23</v>
+        <v>-2.2</v>
       </c>
       <c r="P7" t="n">
-        <v>-11.67</v>
+        <v>-15.36</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>高配</t>
+          <t>低配</t>
         </is>
       </c>
       <c r="R7" t="n">
@@ -996,10 +996,10 @@
         <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="V7" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
@@ -1019,19 +1019,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2.0936</v>
+        <v>2.1156</v>
       </c>
       <c r="D8" t="n">
-        <v>14.85</v>
+        <v>15.13</v>
       </c>
       <c r="E8" t="n">
-        <v>65</v>
+        <v>73.52</v>
       </c>
       <c r="F8" t="n">
-        <v>28.88</v>
+        <v>29.82</v>
       </c>
       <c r="G8" t="n">
-        <v>48.8</v>
+        <v>53.18</v>
       </c>
       <c r="H8" t="n">
         <v>1.88</v>
@@ -1052,13 +1052,13 @@
         <v>-0.55</v>
       </c>
       <c r="N8" t="n">
-        <v>0.65</v>
+        <v>-0.49</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.5</v>
+        <v>-0.19</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.36</v>
+        <v>-3.58</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -1098,19 +1098,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>3.2137</v>
+        <v>3.22</v>
       </c>
       <c r="D9" t="n">
-        <v>19.98</v>
+        <v>21.15</v>
       </c>
       <c r="E9" t="n">
-        <v>10.61</v>
+        <v>28.3</v>
       </c>
       <c r="F9" t="n">
-        <v>38.84</v>
+        <v>36.57</v>
       </c>
       <c r="G9" t="n">
-        <v>85.65000000000001</v>
+        <v>79.14</v>
       </c>
       <c r="H9" t="n">
         <v>3.27</v>
@@ -1131,13 +1131,13 @@
         <v>-1.28</v>
       </c>
       <c r="N9" t="n">
-        <v>1.14</v>
+        <v>-0.45</v>
       </c>
       <c r="O9" t="n">
-        <v>-4.04</v>
+        <v>-1.89</v>
       </c>
       <c r="P9" t="n">
-        <v>-17.26</v>
+        <v>-18.96</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -1177,19 +1177,19 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.512</v>
+        <v>0.5145</v>
       </c>
       <c r="D10" t="n">
-        <v>24.93</v>
+        <v>25.13</v>
       </c>
       <c r="E10" t="n">
-        <v>67.54000000000001</v>
+        <v>69.09</v>
       </c>
       <c r="F10" t="n">
-        <v>41.31</v>
+        <v>44.33</v>
       </c>
       <c r="G10" t="n">
-        <v>62.76</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="H10" t="n">
         <v>2.72</v>
@@ -1210,17 +1210,17 @@
         <v>-0.06</v>
       </c>
       <c r="N10" t="n">
-        <v>2.53</v>
+        <v>2.57</v>
       </c>
       <c r="O10" t="n">
-        <v>5.71</v>
+        <v>3.88</v>
       </c>
       <c r="P10" t="n">
-        <v>-3.95</v>
+        <v>-5.16</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>平配</t>
+          <t>高配</t>
         </is>
       </c>
       <c r="R10" t="n">
@@ -1233,10 +1233,10 @@
         <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
@@ -1256,19 +1256,19 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.7734</v>
+        <v>0.786</v>
       </c>
       <c r="D11" t="n">
-        <v>32.45</v>
+        <v>34.37</v>
       </c>
       <c r="E11" t="n">
-        <v>88.92</v>
+        <v>95.02</v>
       </c>
       <c r="F11" t="n">
-        <v>33.55</v>
+        <v>37.1</v>
       </c>
       <c r="G11" t="n">
-        <v>46.73</v>
+        <v>53.82</v>
       </c>
       <c r="H11" t="n">
         <v>1.85</v>
@@ -1289,21 +1289,21 @@
         <v>-1.8</v>
       </c>
       <c r="N11" t="n">
-        <v>2.55</v>
+        <v>1.33</v>
       </c>
       <c r="O11" t="n">
-        <v>5.76</v>
+        <v>2.73</v>
       </c>
       <c r="P11" t="n">
-        <v>-5.7</v>
+        <v>-6.81</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>平配</t>
+          <t>低配</t>
         </is>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -1315,7 +1315,7 @@
         <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
@@ -1335,19 +1335,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>6.3566</v>
+        <v>6.298</v>
       </c>
       <c r="D12" t="n">
-        <v>33.76</v>
+        <v>32.3</v>
       </c>
       <c r="E12" t="n">
-        <v>69.98999999999999</v>
+        <v>61.58</v>
       </c>
       <c r="F12" t="n">
-        <v>54.75</v>
+        <v>52.73</v>
       </c>
       <c r="G12" t="n">
-        <v>96.48999999999999</v>
+        <v>94.43000000000001</v>
       </c>
       <c r="H12" t="n">
         <v>2.51</v>
@@ -1368,13 +1368,13 @@
         <v>0.89</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.43</v>
+        <v>-2.08</v>
       </c>
       <c r="O12" t="n">
-        <v>4.22</v>
+        <v>-0.16</v>
       </c>
       <c r="P12" t="n">
-        <v>-11.45</v>
+        <v>-14.48</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -1414,19 +1414,19 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2.4189</v>
+        <v>2.4318</v>
       </c>
       <c r="D13" t="n">
-        <v>20.98</v>
+        <v>21.87</v>
       </c>
       <c r="E13" t="n">
-        <v>54.24</v>
+        <v>59.84</v>
       </c>
       <c r="F13" t="n">
-        <v>28.8</v>
+        <v>27.47</v>
       </c>
       <c r="G13" t="n">
-        <v>48.72</v>
+        <v>44.9</v>
       </c>
       <c r="H13" t="n">
         <v>3.46</v>
@@ -1447,13 +1447,13 @@
         <v>-0.3</v>
       </c>
       <c r="N13" t="n">
-        <v>1.7</v>
+        <v>0.2</v>
       </c>
       <c r="O13" t="n">
-        <v>-1.79</v>
+        <v>-1.23</v>
       </c>
       <c r="P13" t="n">
-        <v>4.06</v>
+        <v>3.38</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
@@ -1493,19 +1493,19 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1.8702</v>
+        <v>1.8674</v>
       </c>
       <c r="D14" t="n">
-        <v>17.06</v>
+        <v>16.96</v>
       </c>
       <c r="E14" t="n">
-        <v>79.81</v>
+        <v>78.66</v>
       </c>
       <c r="F14" t="n">
-        <v>21.02</v>
+        <v>22.2</v>
       </c>
       <c r="G14" t="n">
-        <v>50.64</v>
+        <v>56.29</v>
       </c>
       <c r="H14" t="n">
         <v>3.4</v>
@@ -1526,17 +1526,17 @@
         <v>0.24</v>
       </c>
       <c r="N14" t="n">
-        <v>1.59</v>
+        <v>-1.03</v>
       </c>
       <c r="O14" t="n">
-        <v>0.42</v>
+        <v>-0.97</v>
       </c>
       <c r="P14" t="n">
-        <v>-5.79</v>
+        <v>-8.08</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>高配</t>
+          <t>平配</t>
         </is>
       </c>
       <c r="R14" t="n">
@@ -1549,10 +1549,10 @@
         <v>1</v>
       </c>
       <c r="U14" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="V14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
@@ -1572,19 +1572,19 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.8423</v>
+        <v>0.8293</v>
       </c>
       <c r="D15" t="n">
-        <v>20.13</v>
+        <v>17.23</v>
       </c>
       <c r="E15" t="n">
-        <v>66.90000000000001</v>
+        <v>59.29</v>
       </c>
       <c r="F15" t="n">
-        <v>35.1</v>
+        <v>42.07</v>
       </c>
       <c r="G15" t="n">
-        <v>57.89</v>
+        <v>72.77</v>
       </c>
       <c r="H15" t="n">
         <v>-0.27</v>
@@ -1605,17 +1605,17 @@
         <v>-0.33</v>
       </c>
       <c r="N15" t="n">
-        <v>2.59</v>
+        <v>-1.1</v>
       </c>
       <c r="O15" t="n">
-        <v>4.7</v>
+        <v>0.25</v>
       </c>
       <c r="P15" t="n">
-        <v>-11.88</v>
+        <v>-15.9</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>平配</t>
+          <t>低配</t>
         </is>
       </c>
       <c r="R15" t="n">
@@ -1628,10 +1628,10 @@
         <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
@@ -1651,19 +1651,19 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.8192</v>
+        <v>0.8341</v>
       </c>
       <c r="D16" t="n">
-        <v>34.96</v>
+        <v>34.79</v>
       </c>
       <c r="E16" t="n">
-        <v>58.75</v>
+        <v>57.87</v>
       </c>
       <c r="F16" t="n">
-        <v>34.91</v>
+        <v>35.35</v>
       </c>
       <c r="G16" t="n">
-        <v>58.61</v>
+        <v>59.63</v>
       </c>
       <c r="H16" t="n">
         <v>2.09</v>
@@ -1684,13 +1684,13 @@
         <v>3.38</v>
       </c>
       <c r="N16" t="n">
-        <v>3.41</v>
+        <v>2.33</v>
       </c>
       <c r="O16" t="n">
-        <v>1.06</v>
+        <v>0.97</v>
       </c>
       <c r="P16" t="n">
-        <v>-17.46</v>
+        <v>-19.3</v>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
@@ -1730,19 +1730,19 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.4965</v>
+        <v>0.5041</v>
       </c>
       <c r="D17" t="n">
-        <v>40.41</v>
+        <v>41.8</v>
       </c>
       <c r="E17" t="n">
-        <v>21.69</v>
+        <v>25.85</v>
       </c>
       <c r="F17" t="n">
-        <v>36.99</v>
+        <v>39.67</v>
       </c>
       <c r="G17" t="n">
-        <v>28.87</v>
+        <v>35.03</v>
       </c>
       <c r="H17" t="n">
         <v>2.58</v>
@@ -1763,13 +1763,13 @@
         <v>-0.58</v>
       </c>
       <c r="N17" t="n">
-        <v>3.32</v>
+        <v>2.83</v>
       </c>
       <c r="O17" t="n">
-        <v>4.96</v>
+        <v>3.38</v>
       </c>
       <c r="P17" t="n">
-        <v>-13.84</v>
+        <v>-15.49</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
@@ -1809,19 +1809,19 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>5.1334</v>
+        <v>5.3188</v>
       </c>
       <c r="D18" t="n">
-        <v>6.17</v>
+        <v>6.38</v>
       </c>
       <c r="E18" t="n">
-        <v>72.84</v>
+        <v>82.20999999999999</v>
       </c>
       <c r="F18" t="n">
-        <v>12.28</v>
+        <v>13.86</v>
       </c>
       <c r="G18" t="n">
-        <v>73.44</v>
+        <v>82.8</v>
       </c>
       <c r="H18" t="n">
         <v>4.97</v>
@@ -1842,17 +1842,17 @@
         <v>-0.21</v>
       </c>
       <c r="N18" t="n">
-        <v>0.02</v>
+        <v>2.19</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.38</v>
+        <v>5.88</v>
       </c>
       <c r="P18" t="n">
-        <v>-7.55</v>
+        <v>-3.14</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>低配</t>
+          <t>平配</t>
         </is>
       </c>
       <c r="R18" t="n">
@@ -1865,10 +1865,10 @@
         <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
@@ -1888,19 +1888,19 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>5.011</v>
+        <v>5.0816</v>
       </c>
       <c r="D19" t="n">
-        <v>11.58</v>
+        <v>9.66</v>
       </c>
       <c r="E19" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>17.92</v>
+        <v>19.55</v>
       </c>
       <c r="G19" t="n">
-        <v>38.2</v>
+        <v>46.66</v>
       </c>
       <c r="H19" t="n">
         <v>4.27</v>
@@ -1921,13 +1921,13 @@
         <v>2.03</v>
       </c>
       <c r="N19" t="n">
-        <v>3.94</v>
+        <v>-0.01</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.1</v>
+        <v>-0.2</v>
       </c>
       <c r="P19" t="n">
-        <v>-11.25</v>
+        <v>-13.55</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
@@ -1967,19 +1967,19 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.2021</v>
+        <v>0.201</v>
       </c>
       <c r="D20" t="n">
-        <v>93.7</v>
+        <v>79.5</v>
       </c>
       <c r="E20" t="n">
-        <v>93.98</v>
+        <v>92.17</v>
       </c>
       <c r="F20" t="n">
-        <v>55.43</v>
+        <v>49.83</v>
       </c>
       <c r="G20" t="n">
-        <v>90.59</v>
+        <v>86.15000000000001</v>
       </c>
       <c r="H20" t="n">
         <v>2.04</v>
@@ -2000,13 +2000,13 @@
         <v>-3.88</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.7</v>
+        <v>-0.3</v>
       </c>
       <c r="O20" t="n">
-        <v>10.74</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="P20" t="n">
-        <v>34.83</v>
+        <v>18.44</v>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
@@ -2017,7 +2017,7 @@
         <v>-1</v>
       </c>
       <c r="S20" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
         <v>1</v>
@@ -2026,7 +2026,7 @@
         <v>-1</v>
       </c>
       <c r="V20" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
@@ -2046,19 +2046,19 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.883</v>
+        <v>0.8707</v>
       </c>
       <c r="D21" t="n">
-        <v>36.03</v>
+        <v>36.71</v>
       </c>
       <c r="E21" t="n">
-        <v>94.14</v>
+        <v>94.7</v>
       </c>
       <c r="F21" t="n">
-        <v>35.75</v>
+        <v>36.57</v>
       </c>
       <c r="G21" t="n">
-        <v>66.34999999999999</v>
+        <v>67.83</v>
       </c>
       <c r="H21" t="n">
         <v>0.8</v>
@@ -2079,17 +2079,17 @@
         <v>1.23</v>
       </c>
       <c r="N21" t="n">
-        <v>1.97</v>
+        <v>2.1</v>
       </c>
       <c r="O21" t="n">
-        <v>6.86</v>
+        <v>2.15</v>
       </c>
       <c r="P21" t="n">
-        <v>21.4</v>
+        <v>16.36</v>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>低配</t>
+          <t>平配</t>
         </is>
       </c>
       <c r="R21" t="n">
@@ -2102,10 +2102,10 @@
         <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V21" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="W21" t="inlineStr">
         <is>
@@ -2125,19 +2125,19 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1.2957</v>
+        <v>1.2942</v>
       </c>
       <c r="D22" t="n">
-        <v>13.42</v>
+        <v>14.63</v>
       </c>
       <c r="E22" t="n">
-        <v>90.42</v>
+        <v>95.18000000000001</v>
       </c>
       <c r="F22" t="n">
-        <v>29.6</v>
+        <v>29.47</v>
       </c>
       <c r="G22" t="n">
-        <v>47.77</v>
+        <v>47.37</v>
       </c>
       <c r="H22" t="n">
         <v>1.38</v>
@@ -2158,13 +2158,13 @@
         <v>0.57</v>
       </c>
       <c r="N22" t="n">
-        <v>1.8</v>
+        <v>-0.68</v>
       </c>
       <c r="O22" t="n">
-        <v>3.2</v>
+        <v>0.29</v>
       </c>
       <c r="P22" t="n">
-        <v>-3.59</v>
+        <v>-5.46</v>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
@@ -2181,10 +2181,10 @@
         <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="V22" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="W22" t="inlineStr">
         <is>
@@ -2204,19 +2204,19 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>8.4611</v>
+        <v>8.2722</v>
       </c>
       <c r="D23" t="n">
-        <v>31.78</v>
+        <v>29.39</v>
       </c>
       <c r="E23" t="n">
-        <v>49.01</v>
+        <v>39.53</v>
       </c>
       <c r="F23" t="n">
-        <v>39.05</v>
+        <v>38.43</v>
       </c>
       <c r="G23" t="n">
-        <v>52.39</v>
+        <v>51.51</v>
       </c>
       <c r="H23" t="n">
         <v>2.58</v>
@@ -2237,13 +2237,13 @@
         <v>0.15</v>
       </c>
       <c r="N23" t="n">
-        <v>-2.87</v>
+        <v>-5.44</v>
       </c>
       <c r="O23" t="n">
-        <v>0.67</v>
+        <v>-7.79</v>
       </c>
       <c r="P23" t="n">
-        <v>19.13</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
@@ -2283,19 +2283,19 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>6.1859</v>
+        <v>6.2326</v>
       </c>
       <c r="D24" t="n">
-        <v>43.64</v>
+        <v>42.32</v>
       </c>
       <c r="E24" t="n">
-        <v>93.98</v>
+        <v>90.83</v>
       </c>
       <c r="F24" t="n">
-        <v>39.48</v>
+        <v>38.82</v>
       </c>
       <c r="G24" t="n">
-        <v>54.55</v>
+        <v>53.58</v>
       </c>
       <c r="H24" t="n">
         <v>2.34</v>
@@ -2316,13 +2316,13 @@
         <v>0.72</v>
       </c>
       <c r="N24" t="n">
-        <v>0.36</v>
+        <v>0.48</v>
       </c>
       <c r="O24" t="n">
-        <v>8.4</v>
+        <v>1.04</v>
       </c>
       <c r="P24" t="n">
-        <v>19.08</v>
+        <v>14.24</v>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
@@ -2362,19 +2362,19 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>2.6109</v>
+        <v>2.6397</v>
       </c>
       <c r="D25" t="n">
-        <v>59.69</v>
+        <v>54.82</v>
       </c>
       <c r="E25" t="n">
-        <v>50.75</v>
+        <v>31.54</v>
       </c>
       <c r="F25" t="n">
-        <v>31.28</v>
+        <v>30.16</v>
       </c>
       <c r="G25" t="n">
-        <v>44.1</v>
+        <v>40.45</v>
       </c>
       <c r="H25" t="n">
         <v>0.67</v>
@@ -2395,17 +2395,17 @@
         <v>1.16</v>
       </c>
       <c r="N25" t="n">
-        <v>1.72</v>
+        <v>3.49</v>
       </c>
       <c r="O25" t="n">
-        <v>3.28</v>
+        <v>0.41</v>
       </c>
       <c r="P25" t="n">
-        <v>-8.06</v>
+        <v>-8.66</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>平配</t>
+          <t>高配</t>
         </is>
       </c>
       <c r="R25" t="n">
@@ -2418,10 +2418,10 @@
         <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W25" t="inlineStr">
         <is>
@@ -2441,19 +2441,19 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>4.7258</v>
+        <v>4.8667</v>
       </c>
       <c r="D26" t="n">
-        <v>67.65000000000001</v>
+        <v>63.16</v>
       </c>
       <c r="E26" t="n">
-        <v>63.97</v>
+        <v>52.49</v>
       </c>
       <c r="F26" t="n">
-        <v>39.09</v>
+        <v>37.72</v>
       </c>
       <c r="G26" t="n">
-        <v>33.57</v>
+        <v>30.81</v>
       </c>
       <c r="H26" t="n">
         <v>-0.5</v>
@@ -2474,17 +2474,17 @@
         <v>0.71</v>
       </c>
       <c r="N26" t="n">
-        <v>1.38</v>
+        <v>3.42</v>
       </c>
       <c r="O26" t="n">
-        <v>0.41</v>
+        <v>-4.09</v>
       </c>
       <c r="P26" t="n">
-        <v>-13.6</v>
+        <v>-17.38</v>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>高配</t>
+          <t>低配</t>
         </is>
       </c>
       <c r="R26" t="n">
@@ -2497,10 +2497,10 @@
         <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="V26" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="W26" t="inlineStr">
         <is>
@@ -2520,19 +2520,19 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1.6308</v>
+        <v>1.7163</v>
       </c>
       <c r="D27" t="n">
-        <v>34.73</v>
+        <v>35.1</v>
       </c>
       <c r="E27" t="n">
-        <v>44.73</v>
+        <v>46.4</v>
       </c>
       <c r="F27" t="n">
-        <v>35.42</v>
+        <v>39.23</v>
       </c>
       <c r="G27" t="n">
-        <v>29.59</v>
+        <v>39.57</v>
       </c>
       <c r="H27" t="n">
         <v>1.31</v>
@@ -2553,13 +2553,13 @@
         <v>2.16</v>
       </c>
       <c r="N27" t="n">
-        <v>0.22</v>
+        <v>3.8</v>
       </c>
       <c r="O27" t="n">
-        <v>-2.94</v>
+        <v>-4.19</v>
       </c>
       <c r="P27" t="n">
-        <v>-14.27</v>
+        <v>-13.58</v>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
@@ -2599,19 +2599,19 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>5.8119</v>
+        <v>5.8025</v>
       </c>
       <c r="D28" t="n">
-        <v>57.04</v>
+        <v>49.86</v>
       </c>
       <c r="E28" t="n">
-        <v>93.27</v>
+        <v>86.72</v>
       </c>
       <c r="F28" t="n">
-        <v>49.14</v>
+        <v>45.81</v>
       </c>
       <c r="G28" t="n">
-        <v>70.26000000000001</v>
+        <v>66.8</v>
       </c>
       <c r="H28" t="n">
         <v>1.95</v>
@@ -2632,21 +2632,21 @@
         <v>4.72</v>
       </c>
       <c r="N28" t="n">
-        <v>-3.13</v>
+        <v>-0.5</v>
       </c>
       <c r="O28" t="n">
-        <v>10.13</v>
+        <v>-0.57</v>
       </c>
       <c r="P28" t="n">
-        <v>85.06999999999999</v>
+        <v>68.81999999999999</v>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>低配</t>
+          <t>平配</t>
         </is>
       </c>
       <c r="R28" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -2658,7 +2658,7 @@
         <v>-1</v>
       </c>
       <c r="V28" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="W28" t="inlineStr">
         <is>
@@ -2678,19 +2678,19 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.9446</v>
+        <v>0.9435</v>
       </c>
       <c r="D29" t="n">
-        <v>22.77</v>
+        <v>19.31</v>
       </c>
       <c r="E29" t="n">
-        <v>98.59</v>
+        <v>87.43000000000001</v>
       </c>
       <c r="F29" t="n">
-        <v>45.46</v>
+        <v>52.87</v>
       </c>
       <c r="G29" t="n">
-        <v>82.79000000000001</v>
+        <v>90.7</v>
       </c>
       <c r="H29" t="n">
         <v>3.59</v>
@@ -2711,13 +2711,13 @@
         <v>1.2</v>
       </c>
       <c r="N29" t="n">
-        <v>5.13</v>
+        <v>0.11</v>
       </c>
       <c r="O29" t="n">
-        <v>9.9</v>
+        <v>10.22</v>
       </c>
       <c r="P29" t="n">
-        <v>31.81</v>
+        <v>28.02</v>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
@@ -2725,10 +2725,10 @@
         </is>
       </c>
       <c r="R29" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="T29" t="n">
         <v>1</v>
@@ -2757,19 +2757,19 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>1.1858</v>
+        <v>1.1932</v>
       </c>
       <c r="D30" t="n">
-        <v>21.36</v>
+        <v>17.48</v>
       </c>
       <c r="E30" t="n">
-        <v>94.01000000000001</v>
+        <v>79.17</v>
       </c>
       <c r="F30" t="n">
-        <v>28.39</v>
+        <v>29.59</v>
       </c>
       <c r="G30" t="n">
-        <v>72.31999999999999</v>
+        <v>75.55</v>
       </c>
       <c r="H30" t="n">
         <v>2.79</v>
@@ -2790,21 +2790,21 @@
         <v>3.12</v>
       </c>
       <c r="N30" t="n">
-        <v>3.23</v>
+        <v>2.8</v>
       </c>
       <c r="O30" t="n">
-        <v>8.75</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="P30" t="n">
-        <v>25.75</v>
+        <v>23.68</v>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>平配</t>
+          <t>高配</t>
         </is>
       </c>
       <c r="R30" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -2816,7 +2816,7 @@
         <v>0</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W30" t="inlineStr">
         <is>
@@ -2836,19 +2836,19 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.8045</v>
+        <v>0.8057</v>
       </c>
       <c r="D31" t="n">
-        <v>26.31</v>
+        <v>25.41</v>
       </c>
       <c r="E31" t="n">
-        <v>80.90000000000001</v>
+        <v>77.42</v>
       </c>
       <c r="F31" t="n">
-        <v>30.74</v>
+        <v>30.59</v>
       </c>
       <c r="G31" t="n">
-        <v>51.11</v>
+        <v>50.58</v>
       </c>
       <c r="H31" t="n">
         <v>1.64</v>
@@ -2869,17 +2869,17 @@
         <v>1.69</v>
       </c>
       <c r="N31" t="n">
-        <v>1.98</v>
+        <v>-0.04</v>
       </c>
       <c r="O31" t="n">
-        <v>6.79</v>
+        <v>1</v>
       </c>
       <c r="P31" t="n">
-        <v>2.17</v>
+        <v>-0.63</v>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>平配</t>
+          <t>低配</t>
         </is>
       </c>
       <c r="R31" t="n">
@@ -2892,10 +2892,10 @@
         <v>0</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="V31" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="W31" t="inlineStr">
         <is>
@@ -2915,19 +2915,19 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.1823</v>
+        <v>0.1838</v>
       </c>
       <c r="D32" t="n">
-        <v>30.39</v>
+        <v>28.48</v>
       </c>
       <c r="E32" t="n">
-        <v>16.55</v>
+        <v>6.41</v>
       </c>
       <c r="F32" t="n">
-        <v>38.72</v>
+        <v>41.47</v>
       </c>
       <c r="G32" t="n">
-        <v>61.58</v>
+        <v>68.02</v>
       </c>
       <c r="H32" t="n">
         <v>4.07</v>
@@ -2948,21 +2948,21 @@
         <v>0.09</v>
       </c>
       <c r="N32" t="n">
-        <v>2.94</v>
+        <v>0.49</v>
       </c>
       <c r="O32" t="n">
-        <v>-2.54</v>
+        <v>-0.9</v>
       </c>
       <c r="P32" t="n">
-        <v>-27.31</v>
+        <v>-28.24</v>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>平配</t>
+          <t>高配</t>
         </is>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -2974,7 +2974,7 @@
         <v>-1</v>
       </c>
       <c r="V32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W32" t="inlineStr">
         <is>
